--- a/louvers/files/reference_xls/price_xls/aerofoil_af250.xlsx
+++ b/louvers/files/reference_xls/price_xls/aerofoil_af250.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/files/reference_xls/price_xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/louvers/files/reference_xls/price_xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7F8DF4-E56E-7B46-9046-F35620285633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B069B8D9-7C38-3A4B-9419-9D89DA163037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" xr2:uid="{C496E742-E4DE-5F45-8BA5-297BA30B28EC}"/>
   </bookViews>
@@ -1079,39 +1079,39 @@
       </c>
       <c r="B2" s="10">
         <f>C2/10.76391</f>
-        <v>2023.4282895341935</v>
+        <v>2225.771118487613</v>
       </c>
       <c r="C2" s="11">
         <f>((1000/B8)*2.904)*A8</f>
-        <v>21780</v>
+        <v>23958</v>
       </c>
       <c r="D2" s="12">
         <f>+A8*2.904</f>
-        <v>2178</v>
+        <v>2395.7999999999997</v>
       </c>
       <c r="E2" s="22">
         <f>F2/10.76391</f>
-        <v>2210.6275479820997</v>
+        <v>2412.9703769355187</v>
       </c>
       <c r="F2" s="23">
         <f>C2+((((520*0.03937)*39.37)*(1000/B8))*0.25)</f>
-        <v>23794.99597</v>
+        <v>25972.99597</v>
       </c>
       <c r="G2" s="24">
         <f>+D2+(((520/25.4)*39.37008)*0.25)</f>
-        <v>2379.500409448819</v>
+        <v>2597.3004094488188</v>
       </c>
       <c r="H2" s="34">
         <f>I2/10.76391</f>
-        <v>2547.5862131883305</v>
+        <v>2749.92904214175</v>
       </c>
       <c r="I2" s="35">
         <f>C2+((((520*0.03937)*39.37)*(1000/B8))*0.7)</f>
-        <v>27421.988716</v>
+        <v>29599.988716</v>
       </c>
       <c r="J2" s="36">
         <f>+D2+(((520/25.4)*39.37008)*0.6)</f>
-        <v>2661.6009826771656</v>
+        <v>2879.4009826771653</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1120,39 +1120,39 @@
       </c>
       <c r="B3" s="13">
         <f>C3/10.76391</f>
-        <v>75.530174444044974</v>
+        <v>83.083191888449477</v>
       </c>
       <c r="C3" s="14">
         <f>((((1000/B8)*2)*50/1000)*1.084)*A8</f>
-        <v>813</v>
+        <v>894.30000000000007</v>
       </c>
       <c r="D3" s="15">
         <f>+A8*1.365</f>
-        <v>1023.75</v>
+        <v>1126.125</v>
       </c>
       <c r="E3" s="25">
         <f>F3/10.76391</f>
-        <v>84.890137366440271</v>
+        <v>92.443154810844774</v>
       </c>
       <c r="F3" s="26">
         <f>C3+((((260*0.03937)*39.37)*((1000/B8)*2)*50/1000)*0.25)</f>
-        <v>913.7497985</v>
+        <v>995.04979850000007</v>
       </c>
       <c r="G3" s="27">
         <f>+D3+(((166/25.4)*39.37008)*0.25)</f>
-        <v>1088.0751307086614</v>
+        <v>1190.4501307086614</v>
       </c>
       <c r="H3" s="37">
         <f>I3/10.76391</f>
-        <v>101.73807062675182</v>
+        <v>109.29108807115631</v>
       </c>
       <c r="I3" s="38">
         <f>C3+((((260*0.03937)*39.37)*((1000/B8)*2)*(50/1000))*0.7)</f>
-        <v>1095.0994358</v>
+        <v>1176.3994358</v>
       </c>
       <c r="J3" s="39">
         <f>+D3+(((166/25.4)*39.37008)*0.6)</f>
-        <v>1178.1303137007874</v>
+        <v>1280.5053137007874</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1161,39 +1161,39 @@
       </c>
       <c r="B4" s="51">
         <f>C4/10.76391</f>
-        <v>95.109490882030798</v>
+        <v>104.62043997023387</v>
       </c>
       <c r="C4" s="52">
         <f>((((1000/B8)*2)*50/1000)*1.365)*A8</f>
-        <v>1023.75</v>
+        <v>1126.125</v>
       </c>
       <c r="D4" s="53">
         <f>+A8*1.084</f>
-        <v>813</v>
+        <v>894.30000000000007</v>
       </c>
       <c r="E4" s="48">
         <f>F4/10.76391</f>
-        <v>108.64543726211016</v>
+        <v>118.15638635031324</v>
       </c>
       <c r="F4" s="49">
         <f>C4+((((376*0.03937)*39.37)*((1000/B8)*2)*50/1000)*0.25)</f>
-        <v>1169.4497086000001</v>
+        <v>1271.8247086000001</v>
       </c>
       <c r="G4" s="50">
         <f>+D4+(((260/25.4)*39.37008)*0.25)</f>
-        <v>913.75020472440951</v>
+        <v>995.05020472440958</v>
       </c>
       <c r="H4" s="54">
         <f>I4/10.76391</f>
-        <v>133.010140746253</v>
+        <v>142.52108983445606</v>
       </c>
       <c r="I4" s="55">
         <f>C4+((((376*0.03937)*39.37)*((1000/B8)*2)*(50/1000))*0.7)</f>
-        <v>1431.7091840799999</v>
+        <v>1534.0841840799999</v>
       </c>
       <c r="J4" s="56">
         <f>+D4+(((260/25.4)*39.37008)*0.6)</f>
-        <v>1054.8004913385828</v>
+        <v>1136.1004913385827</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="6" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1202,29 +1202,29 @@
       </c>
       <c r="B5" s="16">
         <f>SUM(B2:B4)</f>
-        <v>2194.0679548602693</v>
+        <v>2413.4747503462963</v>
       </c>
       <c r="C5" s="17">
         <f>SUM(C2:C4)</f>
-        <v>23616.75</v>
+        <v>25978.424999999999</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="28">
         <f>SUM(E2:E4)</f>
-        <v>2404.1631226106501</v>
+        <v>2623.5699180966767</v>
       </c>
       <c r="F5" s="29">
         <f>SUM(F2:F4)</f>
-        <v>25878.195477100002</v>
+        <v>28239.870477100001</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="40">
         <f>SUM(H2:H4)</f>
-        <v>2782.3344245613353</v>
+        <v>3001.7412200473623</v>
       </c>
       <c r="I5" s="41">
         <f>SUM(I2:I4)</f>
-        <v>29948.797335879997</v>
+        <v>32310.472335879997</v>
       </c>
       <c r="J5" s="42"/>
     </row>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="8" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>750</v>
+        <v>825</v>
       </c>
       <c r="B8" s="5">
         <v>100</v>
